--- a/artfynd/A 44677-2025 artfynd.xlsx
+++ b/artfynd/A 44677-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129715581</v>
       </c>
       <c r="B2" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44677-2025 artfynd.xlsx
+++ b/artfynd/A 44677-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129715581</v>
       </c>
       <c r="B2" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44677-2025 artfynd.xlsx
+++ b/artfynd/A 44677-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129715581</v>
       </c>
       <c r="B2" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44677-2025 artfynd.xlsx
+++ b/artfynd/A 44677-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129715581</v>
       </c>
       <c r="B2" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44677-2025 artfynd.xlsx
+++ b/artfynd/A 44677-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129715581</v>
       </c>
       <c r="B2" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44677-2025 artfynd.xlsx
+++ b/artfynd/A 44677-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129715581</v>
       </c>
       <c r="B2" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44677-2025 artfynd.xlsx
+++ b/artfynd/A 44677-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129715581</v>
       </c>
       <c r="B2" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44677-2025 artfynd.xlsx
+++ b/artfynd/A 44677-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129715581</v>
       </c>
       <c r="B2" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44677-2025 artfynd.xlsx
+++ b/artfynd/A 44677-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129715581</v>
+        <v>129715561</v>
       </c>
       <c r="B2" t="n">
-        <v>92948</v>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567457</v>
+        <v>567484</v>
       </c>
       <c r="R2" t="n">
-        <v>6507670</v>
+        <v>6507641</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -773,6 +774,301 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129360336</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Marsammasjön, Marsammasjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>567433</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6507644</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129715581</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>567457</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6507670</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129360224</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Marsammasjön, Marsammasjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>567433</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6507644</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44677-2025 artfynd.xlsx
+++ b/artfynd/A 44677-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129715561</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129360336</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129715581</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,8 +1089,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129360224</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>